--- a/methodology_spreadsheet.xlsx
+++ b/methodology_spreadsheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aravindaitipamula/Claude/Projects/AIA_Engineer_assignment/cpg-sales-intelligence/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{268CDD5C-ACAC-7648-8FC7-D6C97999A380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D404F6-DA3B-2E43-BBAD-4F115FA6E2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28800" yWindow="-580" windowWidth="32000" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="88">
   <si>
     <t>⏱  Time Log — Vibe Coding Session</t>
   </si>
@@ -58,15 +58,9 @@
     <t>What You Changed / Overrode</t>
   </si>
   <si>
-    <t>Notes</t>
-  </si>
-  <si>
     <t>Claude Code</t>
   </si>
   <si>
-    <t>Also added dedup logic AI omitted</t>
-  </si>
-  <si>
     <t>TOTAL HOURS</t>
   </si>
   <si>
@@ -274,21 +268,39 @@
     <t>Entire code skeleton</t>
   </si>
   <si>
-    <t>Planning the tasks</t>
+    <t>Planning</t>
   </si>
   <si>
     <t>All the tasks with the required tech stack</t>
   </si>
   <si>
     <t>Researched the techstack and chose the suitable ones for the project</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rewrote _parse_dates() — AI missed multi-format edge case
-Corrected the UI where </t>
   </si>
   <si>
     <t xml:space="preserve">Rewrote _parse_dates() — AI missed multi-format edge case
 Corrected the predictions UI where the correction amount was shown twice. 
+</t>
+  </si>
+  <si>
+    <t>Data Generation, training and prediction</t>
+  </si>
+  <si>
+    <t>Requirement</t>
+  </si>
+  <si>
+    <t>Plan each task and tech stack</t>
+  </si>
+  <si>
+    <t>Folder structure for the python files and code generation for all the requirements</t>
+  </si>
+  <si>
+    <t>Model was predicting for a day revenue generation. Corrected the prompt to generate more data and to predict for a month's revenue.</t>
+  </si>
+  <si>
+    <t>Corrected the code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjusted the start and end dates fot the data generation
 </t>
   </si>
 </sst>
@@ -396,14 +408,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -429,11 +438,26 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -744,234 +768,237 @@
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="6" width="40" customWidth="1"/>
-    <col min="7" max="7" width="30" customWidth="1"/>
+    <col min="5" max="5" width="43.6640625" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
+    <col min="7" max="7" width="56" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="F2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:7" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="14">
+        <v>46191</v>
+      </c>
+      <c r="B3" s="15">
+        <v>2</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="14">
+        <v>46195</v>
+      </c>
+      <c r="B4" s="15">
+        <v>1</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="16" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="12">
-        <v>46191</v>
-      </c>
-      <c r="B3" s="13">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="E4" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="F3" s="2" t="s">
+    </row>
+    <row r="5" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="14">
+        <v>46195</v>
+      </c>
+      <c r="B5" s="15">
+        <v>1</v>
+      </c>
+      <c r="C5" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="12">
-        <v>46195</v>
-      </c>
-      <c r="B4" s="13">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="D5" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+    </row>
+    <row r="7" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="12">
-        <v>46195</v>
-      </c>
-      <c r="B5" s="13">
-        <v>1</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-    </row>
-    <row r="7" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-    </row>
-    <row r="8" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-    </row>
-    <row r="9" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-    </row>
-    <row r="10" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-    </row>
-    <row r="11" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-    </row>
-    <row r="12" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-    </row>
-    <row r="13" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-    </row>
-    <row r="14" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-    </row>
-    <row r="15" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-    </row>
-    <row r="16" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-    </row>
-    <row r="17" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-    </row>
-    <row r="18" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-    </row>
-    <row r="19" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="4">
+      <c r="B19" s="7"/>
+      <c r="C19" s="3">
         <f>SUM(B3:B18)</f>
         <v>4</v>
       </c>
@@ -997,172 +1024,172 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+    </row>
+    <row r="2" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+    </row>
+    <row r="3" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-    </row>
-    <row r="2" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="11" t="s">
+      <c r="B3" s="9">
+        <v>6</v>
+      </c>
+      <c r="C3" s="7"/>
+    </row>
+    <row r="4" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-    </row>
-    <row r="3" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+      <c r="B4" s="9">
+        <v>2</v>
+      </c>
+      <c r="C4" s="7"/>
+    </row>
+    <row r="5" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="10">
-        <v>6</v>
-      </c>
-      <c r="C3" s="8"/>
-    </row>
-    <row r="4" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+      <c r="B5" s="9">
+        <v>1</v>
+      </c>
+      <c r="C5" s="7"/>
+    </row>
+    <row r="6" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B6" s="9">
         <v>2</v>
       </c>
-      <c r="C4" s="8"/>
-    </row>
-    <row r="5" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+      <c r="C6" s="7"/>
+    </row>
+    <row r="7" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B7" s="9">
         <v>1</v>
       </c>
-      <c r="C5" s="8"/>
-    </row>
-    <row r="6" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
+      <c r="C7" s="7"/>
+    </row>
+    <row r="8" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="10">
-        <v>2</v>
-      </c>
-      <c r="C6" s="8"/>
-    </row>
-    <row r="7" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+    </row>
+    <row r="9" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="10">
-        <v>1</v>
-      </c>
-      <c r="C7" s="8"/>
-    </row>
-    <row r="8" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
+      <c r="B9" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="7"/>
+    </row>
+    <row r="10" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-    </row>
-    <row r="9" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
+      <c r="B10" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="7"/>
+    </row>
+    <row r="11" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="8"/>
-    </row>
-    <row r="10" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+    </row>
+    <row r="12" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B12" s="9">
+        <v>95</v>
+      </c>
+      <c r="C12" s="7"/>
+    </row>
+    <row r="13" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="9">
+        <v>5</v>
+      </c>
+      <c r="C13" s="7"/>
+    </row>
+    <row r="14" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="9">
+        <v>0</v>
+      </c>
+      <c r="C14" s="7"/>
+    </row>
+    <row r="15" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+    </row>
+    <row r="16" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="7"/>
+    </row>
+    <row r="17" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="8"/>
-    </row>
-    <row r="11" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-    </row>
-    <row r="12" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="10">
-        <v>95</v>
-      </c>
-      <c r="C12" s="8"/>
-    </row>
-    <row r="13" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="10">
-        <v>5</v>
-      </c>
-      <c r="C13" s="8"/>
-    </row>
-    <row r="14" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="10">
-        <v>0</v>
-      </c>
-      <c r="C14" s="8"/>
-    </row>
-    <row r="15" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-    </row>
-    <row r="16" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
+      <c r="C17" s="7"/>
+    </row>
+    <row r="18" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+    </row>
+    <row r="19" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="7"/>
+    </row>
+    <row r="20" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="8"/>
-    </row>
-    <row r="17" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" s="8"/>
-    </row>
-    <row r="18" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-    </row>
-    <row r="19" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" s="8"/>
-    </row>
-    <row r="20" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" s="8"/>
+      <c r="C20" s="7"/>
     </row>
     <row r="21" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
@@ -1205,238 +1232,238 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
+      <c r="A1" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
     </row>
     <row r="2" spans="1:6" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="5">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="C3" s="5" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="6">
-        <v>1</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="6" t="s">
+    </row>
+    <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="C4" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="C5" s="5" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="F5" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E5" s="6" t="s">
+    </row>
+    <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="C6" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="F6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E6" s="3" t="s">
+    </row>
+    <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="5">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="C7" s="5" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="6">
-        <v>5</v>
-      </c>
-      <c r="B7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="F7" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="6" t="s">
+    </row>
+    <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="C8" s="2" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
-        <v>6</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="F8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E8" s="3" t="s">
+    </row>
+    <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="C9" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="6">
-        <v>7</v>
-      </c>
-      <c r="B9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="F9" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="10" spans="1:6" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:6" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
     </row>
     <row r="16" spans="1:6" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
     </row>
     <row r="17" spans="1:6" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/methodology_spreadsheet.xlsx
+++ b/methodology_spreadsheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aravindaitipamula/Claude/Projects/AIA_Engineer_assignment/cpg-sales-intelligence/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D404F6-DA3B-2E43-BBAD-4F115FA6E2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F366FD8E-8F16-4F40-BCF2-89CD7E9950BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28800" yWindow="-580" windowWidth="32000" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="94">
   <si>
     <t>⏱  Time Log — Vibe Coding Session</t>
   </si>
@@ -282,9 +282,6 @@
 </t>
   </si>
   <si>
-    <t>Data Generation, training and prediction</t>
-  </si>
-  <si>
     <t>Requirement</t>
   </si>
   <si>
@@ -302,13 +299,34 @@
   <si>
     <t xml:space="preserve">Adjusted the start and end dates fot the data generation
 </t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>Writing numpy datatypes into postgres causing an issue</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Data input to LLM API is not sufficient to get better answers out of it.</t>
+  </si>
+  <si>
+    <t>Added more queries to generate relevant data to feed the LLM</t>
+  </si>
+  <si>
+    <t>18/06//2026</t>
+  </si>
+  <si>
+    <t>22/06//2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -331,13 +349,6 @@
       <family val="2"/>
     </font>
     <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF595959"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -349,7 +360,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -360,12 +371,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFC00000"/>
         <bgColor rgb="FFC00000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
-        <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -381,7 +386,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -404,60 +409,109 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -774,125 +828,141 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
     </row>
     <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" s="20">
+        <v>2</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="F2" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="14">
-        <v>46191</v>
-      </c>
-      <c r="B3" s="15">
-        <v>2</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="E3" s="16" t="s">
+      <c r="F3" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="20">
+        <v>1</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="F3" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="G3" s="16" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="14">
-        <v>46195</v>
-      </c>
-      <c r="B4" s="15">
-        <v>1</v>
-      </c>
-      <c r="C4" s="16" t="s">
+      <c r="F4" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="G4" s="21" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="17">
+        <v>3</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E5" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="F4" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="G4" s="16" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="14">
-        <v>46195</v>
-      </c>
-      <c r="B5" s="15">
-        <v>1</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" s="16" t="s">
+      <c r="F5" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="15"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E6" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="F6" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="F5" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
+      <c r="G6" s="21" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="7" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="A7" s="16"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="8" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
@@ -994,19 +1064,22 @@
       <c r="G18" s="2"/>
     </row>
     <row r="19" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="7"/>
+      <c r="B19" s="8"/>
       <c r="C19" s="3">
         <f>SUM(B3:B18)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="5">
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="A5:A7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -1024,194 +1097,194 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
     </row>
     <row r="2" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
     </row>
     <row r="3" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="9">
-        <v>6</v>
-      </c>
-      <c r="C3" s="7"/>
+      <c r="B3" s="12">
+        <v>7</v>
+      </c>
+      <c r="C3" s="8"/>
     </row>
     <row r="4" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="12">
         <v>2</v>
       </c>
-      <c r="C4" s="7"/>
+      <c r="C4" s="8"/>
     </row>
     <row r="5" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="12">
         <v>1</v>
       </c>
-      <c r="C5" s="7"/>
+      <c r="C5" s="8"/>
     </row>
     <row r="6" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="9">
-        <v>2</v>
-      </c>
-      <c r="C6" s="7"/>
+      <c r="B6" s="12">
+        <v>3</v>
+      </c>
+      <c r="C6" s="8"/>
     </row>
     <row r="7" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="12">
         <v>1</v>
       </c>
-      <c r="C7" s="7"/>
+      <c r="C7" s="8"/>
     </row>
     <row r="8" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
     </row>
     <row r="9" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="7"/>
+      <c r="C9" s="8"/>
     </row>
     <row r="10" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="7"/>
+      <c r="C10" s="8"/>
     </row>
     <row r="11" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
     </row>
     <row r="12" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="12">
         <v>95</v>
       </c>
-      <c r="C12" s="7"/>
+      <c r="C12" s="8"/>
     </row>
     <row r="13" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="12">
         <v>5</v>
       </c>
-      <c r="C13" s="7"/>
+      <c r="C13" s="8"/>
     </row>
     <row r="14" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="12">
         <v>0</v>
       </c>
-      <c r="C14" s="7"/>
+      <c r="C14" s="8"/>
     </row>
     <row r="15" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
     </row>
     <row r="16" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="7"/>
+      <c r="C16" s="8"/>
     </row>
     <row r="17" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C17" s="7"/>
+      <c r="C17" s="8"/>
     </row>
     <row r="18" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
     </row>
     <row r="19" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="C19" s="7"/>
+      <c r="C19" s="8"/>
     </row>
     <row r="20" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="7"/>
+      <c r="C20" s="8"/>
     </row>
     <row r="21" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="A15:C15"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="A18:C18"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="A8:C8"/>
-    <mergeCell ref="B14:C14"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B3:C3"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="B17:C17"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="B6:C6"/>
   </mergeCells>
@@ -1232,14 +1305,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
     </row>
     <row r="2" spans="1:6" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">

--- a/methodology_spreadsheet.xlsx
+++ b/methodology_spreadsheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aravindaitipamula/Claude/Projects/AIA_Engineer_assignment/cpg-sales-intelligence/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F366FD8E-8F16-4F40-BCF2-89CD7E9950BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D24B35-C15D-2D41-A443-454A4EF780A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="-580" windowWidth="32000" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28800" yWindow="-580" windowWidth="32000" windowHeight="18000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Time Log" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="95">
   <si>
     <t>⏱  Time Log — Vibe Coding Session</t>
   </si>
@@ -61,9 +61,6 @@
     <t>Claude Code</t>
   </si>
   <si>
-    <t>TOTAL HOURS</t>
-  </si>
-  <si>
     <t>📊  Tool Usage Summary</t>
   </si>
   <si>
@@ -118,9 +115,6 @@
     <t>💡 Prompting Patterns</t>
   </si>
   <si>
-    <t>Most Useful AI Prompt Pattern</t>
-  </si>
-  <si>
     <t>Prompt You'd Never Use Again</t>
   </si>
   <si>
@@ -260,9 +254,6 @@
   </si>
   <si>
     <t>Vague single questions like is streamlit better or flask?</t>
-  </si>
-  <si>
-    <t>Read the attached doc. give me a brief plan on the tasks to do along with the techstack preferences and also add remarks to the task on what feedback u would require from my end to bring that task to closure. also mention any task is to be completed by me only. and the approximate ETAS for each tasks</t>
   </si>
   <si>
     <t>Entire code skeleton</t>
@@ -320,6 +311,19 @@
   </si>
   <si>
     <t>22/06//2026</t>
+  </si>
+  <si>
+    <t>Added datatype for int</t>
+  </si>
+  <si>
+    <t>Added datatype corrections for string and float as well</t>
+  </si>
+  <si>
+    <t>Read the attached doc. give me a brief plan on the tasks to do along with the techstack preferences and also add remarks to the task on what feedback u would require from my end to bring that task to closure. also mention any task is to be completed by me only. and the approximate ETAS for each tasks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Most Useful AI Prompt Pattern
+</t>
   </si>
 </sst>
 </file>
@@ -386,7 +390,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -446,6 +450,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -459,9 +472,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -470,8 +480,11 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -480,38 +493,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -839,243 +850,145 @@
       <c r="G1" s="10"/>
     </row>
     <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="F2" s="6" t="s">
+      <c r="E2" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B3" s="20">
+        <v>89</v>
+      </c>
+      <c r="B3" s="6">
         <v>2</v>
       </c>
-      <c r="C3" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="G3" s="21" t="s">
+      <c r="C3" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>79</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B4" s="20">
+        <v>90</v>
+      </c>
+      <c r="B4" s="6">
         <v>1</v>
       </c>
-      <c r="C4" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="D4" s="21" t="s">
+      <c r="C4" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="G4" s="21" t="s">
+      <c r="E4" s="7" t="s">
         <v>80</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="B5" s="17">
+        <v>90</v>
+      </c>
+      <c r="B5" s="11">
         <v>3</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" s="21" t="s">
+      <c r="C5" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="G5" s="21" t="s">
-        <v>86</v>
+      <c r="E5" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="15"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="21" t="s">
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="F6" s="21" t="s">
+      <c r="E6" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="G6" s="21" t="s">
-        <v>89</v>
+      <c r="F6" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="16"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="21" t="s">
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="G7" s="21" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="3">
-        <f>SUM(B3:B18)</f>
-        <v>6</v>
-      </c>
-    </row>
+      <c r="E7" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="17" ht="40" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" ht="40" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A19:B19"/>
+  <mergeCells count="4">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C5:C7"/>
     <mergeCell ref="B5:B7"/>
@@ -1088,205 +1001,170 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="1" max="1" width="50.1640625" customWidth="1"/>
+    <col min="2" max="2" width="51.5" style="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="8"/>
+    </row>
+    <row r="2" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-    </row>
-    <row r="2" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="13" t="s">
+      <c r="B2" s="8"/>
+    </row>
+    <row r="3" spans="1:2" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-    </row>
-    <row r="3" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
+      <c r="B3" s="21">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B4" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="8"/>
+    </row>
+    <row r="9" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="8"/>
-    </row>
-    <row r="4" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="12">
-        <v>2</v>
-      </c>
-      <c r="C4" s="8"/>
-    </row>
-    <row r="5" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="12">
-        <v>1</v>
-      </c>
-      <c r="C5" s="8"/>
-    </row>
-    <row r="6" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="12">
-        <v>3</v>
-      </c>
-      <c r="C6" s="8"/>
-    </row>
-    <row r="7" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="12">
-        <v>1</v>
-      </c>
-      <c r="C7" s="8"/>
-    </row>
-    <row r="8" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-    </row>
-    <row r="9" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
+    </row>
+    <row r="10" spans="1:2" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="8"/>
-    </row>
-    <row r="10" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
+      <c r="B10" s="21" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B11" s="8"/>
+    </row>
+    <row r="12" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="21">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="8"/>
+    </row>
+    <row r="16" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="8"/>
-    </row>
-    <row r="11" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-    </row>
-    <row r="12" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="12">
-        <v>95</v>
-      </c>
-      <c r="C12" s="8"/>
-    </row>
-    <row r="13" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="12">
-        <v>5</v>
-      </c>
-      <c r="C13" s="8"/>
-    </row>
-    <row r="14" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="12">
-        <v>0</v>
-      </c>
-      <c r="C14" s="8"/>
-    </row>
-    <row r="15" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-    </row>
-    <row r="16" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="12" t="s">
+    </row>
+    <row r="18" spans="1:2" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="8"/>
+    </row>
+    <row r="19" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="8"/>
-    </row>
-    <row r="17" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" s="8"/>
-    </row>
-    <row r="18" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-    </row>
-    <row r="19" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" s="8"/>
-    </row>
-    <row r="20" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" s="8"/>
-    </row>
-    <row r="21" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.2"/>
+    </row>
+    <row r="21" spans="1:2" ht="35" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="B6:C6"/>
+  <mergeCells count="6">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A11:B11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1305,8 +1183,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
-        <v>29</v>
+      <c r="A1" s="18" t="s">
+        <v>27</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -1316,42 +1194,42 @@
     </row>
     <row r="2" spans="1:6" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="C3" s="4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="5">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
@@ -1359,39 +1237,39 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>48</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
@@ -1399,39 +1277,39 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E6" s="2" t="s">
+    </row>
+    <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="C7" s="4" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="5">
-        <v>5</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
@@ -1439,39 +1317,39 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="2" t="s">
+    </row>
+    <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="C9" s="4" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="5">
-        <v>7</v>
-      </c>
-      <c r="B9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="E9" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="F9" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="50" customHeight="1" x14ac:dyDescent="0.2">
